--- a/assets/downloads/CotizacionMARIBEL VILMA GONZALES HUANCA.xlsx
+++ b/assets/downloads/CotizacionMARIBEL VILMA GONZALES HUANCA.xlsx
@@ -4,21 +4,21 @@
   <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView activeTab="1" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
     <sheet name="1" sheetId="1" r:id="rId4"/>
     <sheet name="2" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$103</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'1'!$A$1:$M$104</definedName>
   </definedNames>
   <calcPr calcId="999999" calcMode="auto" calcCompleted="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="120">
   <si>
     <t>PRO MUNDO COMEX S.A.C.</t>
   </si>
@@ -53,7 +53,7 @@
     <t>PESO:</t>
   </si>
   <si>
-    <t>0 Kg</t>
+    <t>100 Kg</t>
   </si>
   <si>
     <t>DNI/RUC:</t>
@@ -71,10 +71,13 @@
     <t>TELEFONO:</t>
   </si>
   <si>
+    <t>51 940 469 505</t>
+  </si>
+  <si>
     <t>CLIENTE:</t>
   </si>
   <si>
-    <t>ANTIGUO</t>
+    <t>NUEVO</t>
   </si>
   <si>
     <t>CBM</t>
@@ -113,9 +116,9 @@
     <t>Hola MARIBEL VILMA GONZALES HUANCA 😁 un gusto saludarte!
         A continuación te envío la cotización final de tu importación📋📦.
         🙋‍♂️ PAGO PENDIENTE :
-        ☑️Costo CBM: $0
-        ☑️Impuestos: $560.05
-        ☑️ Total: $560.05
+        ☑️Costo CBM: $332.64
+        ☑️Impuestos: $936.83
+        ☑️ Total: $1269.47
         Pronto le aviso nuevos avances, que tengan buen día🚢
         Último día de pago:</t>
   </si>
@@ -174,48 +177,28 @@
     <t>PRECIO UNIT. (SOLES)</t>
   </si>
   <si>
-    <t>GORRO CON TRENZAS PARA INVIERNO</t>
-  </si>
-  <si>
-    <t>SOMBRERO PARA DAMA</t>
-  </si>
-  <si>
-    <t>SOMBRERO PUNTOS PARA DAMA</t>
-  </si>
-  <si>
-    <t>GORRO DE INVIERNO</t>
-  </si>
-  <si>
-    <t>GORRO DE INVIERNO CAPIBARA</t>
-  </si>
-  <si>
-    <t>GORRO DE INVIERNO HONGUITO</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Calibri Light"/>
-        <b val="true"/>
-        <i val="false"/>
-        <strike val="false"/>
-        <color rgb="FF000000"/>
-        <sz val="14"/>
-        <u val="none"/>
-      </rPr>
-      <t xml:space="preserve">*</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Calibri Light"/>
-        <b val="false"/>
-        <i val="false"/>
-        <strike val="false"/>
-        <color rgb="FF000000"/>
-        <sz val="14"/>
-        <u val="none"/>
-      </rPr>
-      <t xml:space="preserve">Las fechas brindadas son estimadas, estan sujetas a variación.</t>
-    </r>
+    <t>GORRO CON TRENZAS PARA NIÑA</t>
+  </si>
+  <si>
+    <t>SOMBRERO MODELO CON OREJITAS</t>
+  </si>
+  <si>
+    <t>SOMBRERO VINTAGE PARA NIÑA</t>
+  </si>
+  <si>
+    <t>SOMBRERO DE VERANO PARA NIÑAS</t>
+  </si>
+  <si>
+    <t>SOMBRERO MODELO GIRASOL</t>
+  </si>
+  <si>
+    <t>GORRO MODELO LAZO</t>
+  </si>
+  <si>
+    <t>GORRO CON CUELLERA PARA INVIERNO</t>
+  </si>
+  <si>
+    <t>GORRO DE INVIERNO MODELO CASTOR</t>
   </si>
   <si>
     <r>
@@ -539,7 +522,7 @@
     <numFmt numFmtId="172" formatCode="0.00&quot; Kg&quot;"/>
     <numFmt numFmtId="173" formatCode="&quot;S/.&quot; #,##0.00_-"/>
   </numFmts>
-  <fonts count="19">
+  <fonts count="20">
     <font>
       <b val="0"/>
       <i val="0"/>
@@ -707,6 +690,15 @@
       <i val="0"/>
       <strike val="0"/>
       <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="14"/>
       <color rgb="FF000000"/>
       <name val="Calibri Light"/>
@@ -1156,16 +1148,16 @@
     <xf xfId="0" fontId="17" numFmtId="167" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="2" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
-    </xf>
     <xf xfId="0" fontId="18" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="12" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
+    </xf>
+    <xf xfId="0" fontId="19" numFmtId="0" fillId="3" borderId="1" applyFont="1" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
-    <xf xfId="0" fontId="3" numFmtId="171" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" fontId="19" numFmtId="171" fillId="3" borderId="1" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" shrinkToFit="false"/>
     </xf>
     <xf xfId="0" fontId="2" numFmtId="4" fillId="7" borderId="0" applyFont="1" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1">
@@ -1222,7 +1214,7 @@
     <xdr:from>
       <xdr:col>1</xdr:col>
       <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>48</xdr:row>
+      <xdr:row>49</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="1209675" cy="1190625"/>
@@ -1252,7 +1244,7 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>695325</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="4057650" cy="3429000"/>
@@ -1571,7 +1563,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:N100"/>
+  <dimension ref="A1:N101"/>
   <sheetFormatPr defaultRowHeight="14.4" defaultColWidth="10.77734375" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="7.109375" customWidth="true" style="1"/>
@@ -1721,7 +1713,9 @@
       <c r="B10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="16"/>
+      <c r="C10" s="16">
+        <v>41877382</v>
+      </c>
       <c r="D10" s="34"/>
       <c r="E10" s="27" t="s">
         <v>13</v>
@@ -1742,21 +1736,23 @@
       <c r="B11" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="17"/>
+      <c r="C11" s="17" t="s">
+        <v>17</v>
+      </c>
       <c r="D11" s="35"/>
       <c r="E11" s="24" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F11" s="48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G11" s="65"/>
       <c r="H11" s="33"/>
       <c r="I11" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J11" s="95" t="str">
-        <f>'2'!I7</f>
+        <f>'2'!K7</f>
         <v>0</v>
       </c>
       <c r="K11" s="73"/>
@@ -1777,7 +1773,7 @@
     </row>
     <row r="13" spans="1:14">
       <c r="B13" s="66" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" s="66"/>
       <c r="D13" s="66"/>
@@ -1788,15 +1784,15 @@
       <c r="I13" s="66"/>
       <c r="J13" s="66"/>
       <c r="K13" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L13" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14" s="67" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" s="67"/>
       <c r="D14" s="67"/>
@@ -1807,16 +1803,16 @@
       <c r="I14" s="67"/>
       <c r="J14" s="67"/>
       <c r="K14" s="14" t="str">
-        <f>'2'!I11</f>
+        <f>'2'!K11</f>
         <v>0</v>
       </c>
       <c r="L14" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15" s="68" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="68"/>
       <c r="D15" s="68"/>
@@ -1827,16 +1823,16 @@
       <c r="I15" s="68"/>
       <c r="J15" s="68"/>
       <c r="K15" s="15" t="str">
-        <f>'2'!I14 + '2'!I17</f>
+        <f>'2'!K14 + '2'!K17</f>
         <v>0</v>
       </c>
       <c r="L15" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16" s="51" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="51"/>
       <c r="D16" s="51"/>
@@ -1851,7 +1847,7 @@
         <v>0</v>
       </c>
       <c r="L16" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -1882,7 +1878,7 @@
     </row>
     <row r="19" spans="1:14">
       <c r="B19" s="69" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C19" s="69"/>
       <c r="D19" s="69"/>
@@ -1892,18 +1888,18 @@
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
       <c r="J19" s="10" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="K19" s="10" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L19" s="10" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="B20" s="49" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C20" s="49"/>
       <c r="D20" s="49"/>
@@ -1913,23 +1909,23 @@
       <c r="H20" s="49"/>
       <c r="I20" s="49"/>
       <c r="J20" s="20" t="str">
-        <f>MAX('2'!C27:H27)</f>
+        <f>MAX('2'!C27:J27)</f>
         <v>0</v>
       </c>
       <c r="K20" s="14" t="str">
-        <f>'2'!I28</f>
+        <f>'2'!K28</f>
         <v>0</v>
       </c>
       <c r="L20" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="N20" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="21" spans="1:14">
       <c r="B21" s="49" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="49"/>
       <c r="D21" s="49"/>
@@ -1942,16 +1938,16 @@
         <v>0.16</v>
       </c>
       <c r="K21" s="14" t="str">
-        <f>'2'!I29</f>
+        <f>'2'!K29</f>
         <v>0</v>
       </c>
       <c r="L21" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="B22" s="48" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="48"/>
       <c r="D22" s="48"/>
@@ -1964,16 +1960,16 @@
         <v>0.02</v>
       </c>
       <c r="K22" s="14" t="str">
-        <f>'2'!I30</f>
+        <f>'2'!K30</f>
         <v>0</v>
       </c>
       <c r="L22" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="23" spans="1:14">
       <c r="B23" s="51" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="51"/>
       <c r="D23" s="51"/>
@@ -1988,7 +1984,7 @@
         <v>0</v>
       </c>
       <c r="L23" s="29" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="24" spans="1:14">
@@ -2006,7 +2002,7 @@
     </row>
     <row r="25" spans="1:14">
       <c r="B25" s="48" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C25" s="48"/>
       <c r="D25" s="48"/>
@@ -2016,19 +2012,19 @@
       <c r="H25" s="48"/>
       <c r="I25" s="48"/>
       <c r="J25" s="21" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K25" s="15" t="str">
-        <f>'2'!I31</f>
+        <f>'2'!K31</f>
         <v>0</v>
       </c>
       <c r="L25" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26" spans="1:14">
       <c r="B26" s="51" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="51"/>
       <c r="D26" s="51"/>
@@ -2042,7 +2038,7 @@
         <v>0</v>
       </c>
       <c r="L26" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="27" spans="1:14">
@@ -2057,7 +2053,7 @@
     </row>
     <row r="28" spans="1:14" customHeight="1" ht="15.6">
       <c r="B28" s="52" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" s="52"/>
       <c r="D28" s="52"/>
@@ -2068,15 +2064,15 @@
       <c r="I28" s="52"/>
       <c r="J28" s="52"/>
       <c r="K28" s="28" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L28" s="28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="29" spans="1:14">
       <c r="B29" s="49" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C29" s="49"/>
       <c r="D29" s="49"/>
@@ -2091,12 +2087,12 @@
         <v>0</v>
       </c>
       <c r="L29" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="B30" s="49" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C30" s="49"/>
       <c r="D30" s="49"/>
@@ -2107,16 +2103,16 @@
       <c r="I30" s="49"/>
       <c r="J30" s="49"/>
       <c r="K30" s="14" t="str">
-        <f>IF('2'!M7&lt;1, '2'!M7*J11, '2'!M7*J11)</f>
+        <f>IF(J11&lt;1, '2'!O7, '2'!O7*J11)</f>
         <v>0</v>
       </c>
       <c r="L30" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="31" spans="1:14">
       <c r="B31" s="48" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C31" s="48"/>
       <c r="D31" s="48"/>
@@ -2131,12 +2127,12 @@
         <v>0</v>
       </c>
       <c r="L31" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="32" spans="1:14">
       <c r="B32" s="51" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C32" s="51"/>
       <c r="D32" s="51"/>
@@ -2151,7 +2147,7 @@
         <v>0</v>
       </c>
       <c r="L32" s="9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="33" spans="1:14">
@@ -2169,7 +2165,7 @@
     </row>
     <row r="34" spans="1:14">
       <c r="B34" s="59" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C34" s="60"/>
       <c r="D34" s="60"/>
@@ -2184,28 +2180,28 @@
     </row>
     <row r="35" spans="1:14">
       <c r="B35" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C35" s="56" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D35" s="57"/>
       <c r="E35" s="58"/>
       <c r="F35" s="4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G35" s="56" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H35" s="58"/>
       <c r="I35" s="3" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="K35" s="47" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L35" s="47"/>
     </row>
@@ -2214,7 +2210,7 @@
         <v>1</v>
       </c>
       <c r="C36" s="5" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D36" s="5"/>
       <c r="E36" s="5"/>
@@ -2247,7 +2243,7 @@
         <v>2</v>
       </c>
       <c r="C37" s="5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D37" s="5"/>
       <c r="E37" s="5"/>
@@ -2280,7 +2276,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="5" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D38" s="5"/>
       <c r="E38" s="5"/>
@@ -2313,7 +2309,7 @@
         <v>4</v>
       </c>
       <c r="C39" s="5" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D39" s="5"/>
       <c r="E39" s="5"/>
@@ -2346,7 +2342,7 @@
         <v>5</v>
       </c>
       <c r="C40" s="5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D40" s="5"/>
       <c r="E40" s="5"/>
@@ -2378,7 +2374,7 @@
         <v>6</v>
       </c>
       <c r="C41" s="5" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D41" s="5"/>
       <c r="E41" s="5"/>
@@ -2406,59 +2402,118 @@
       <c r="L41" s="31"/>
     </row>
     <row r="42" spans="1:14" customHeight="1" ht="18">
-      <c r="B42" s="92" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" s="91"/>
-      <c r="D42" s="91"/>
-      <c r="E42" s="91"/>
-      <c r="F42" s="93" t="str">
-        <f>SUM(F36:F41)</f>
-        <v>0</v>
-      </c>
-      <c r="G42" s="7"/>
-      <c r="H42" s="7"/>
-      <c r="I42" s="7"/>
-      <c r="J42" s="94" t="str">
-        <f>SUM(J36:J41)</f>
-        <v>0</v>
-      </c>
-      <c r="K42" s="7"/>
-      <c r="L42" s="1"/>
+      <c r="B42" s="91">
+        <v>7</v>
+      </c>
+      <c r="C42" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D42" s="5"/>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5" t="str">
+        <f>'2'!I10</f>
+        <v>0</v>
+      </c>
+      <c r="G42" s="88" t="str">
+        <f>'2'!I8</f>
+        <v>0</v>
+      </c>
+      <c r="H42" s="5"/>
+      <c r="I42" s="88" t="str">
+        <f>'2'!I46</f>
+        <v>0</v>
+      </c>
+      <c r="J42" s="88" t="str">
+        <f>'2'!I44</f>
+        <v>0</v>
+      </c>
+      <c r="K42" s="89" t="str">
+        <f>'2'!I47</f>
+        <v>0</v>
+      </c>
+      <c r="L42" s="3"/>
     </row>
     <row r="43" spans="1:14" customHeight="1" ht="18">
-      <c r="B43" s="64" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" s="64"/>
-      <c r="D43" s="64"/>
-      <c r="E43" s="64"/>
-      <c r="F43" s="64"/>
-      <c r="G43" s="64"/>
-      <c r="H43" s="64"/>
-      <c r="I43" s="64"/>
-      <c r="J43" s="64"/>
-      <c r="K43" s="64"/>
-      <c r="L43" s="64"/>
+      <c r="B43" s="91">
+        <v>8</v>
+      </c>
+      <c r="C43" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D43" s="5"/>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5" t="str">
+        <f>'2'!J10</f>
+        <v>0</v>
+      </c>
+      <c r="G43" s="88" t="str">
+        <f>'2'!J8</f>
+        <v>0</v>
+      </c>
+      <c r="H43" s="5"/>
+      <c r="I43" s="88" t="str">
+        <f>'2'!J46</f>
+        <v>0</v>
+      </c>
+      <c r="J43" s="88" t="str">
+        <f>'2'!J44</f>
+        <v>0</v>
+      </c>
+      <c r="K43" s="89" t="str">
+        <f>'2'!J47</f>
+        <v>0</v>
+      </c>
+      <c r="L43" s="3"/>
     </row>
     <row r="44" spans="1:14" customHeight="1" ht="18">
-      <c r="B44" s="64" t="s">
-        <v>56</v>
-      </c>
-      <c r="C44" s="64"/>
-      <c r="D44" s="64"/>
-      <c r="E44" s="64"/>
-      <c r="F44" s="64"/>
+      <c r="B44" s="93" t="s">
+        <v>37</v>
+      </c>
+      <c r="C44" s="92"/>
+      <c r="D44" s="92"/>
+      <c r="E44" s="92"/>
+      <c r="F44" s="93" t="str">
+        <f>SUM(F36:F43)</f>
+        <v>0</v>
+      </c>
       <c r="G44" s="64"/>
       <c r="H44" s="64"/>
       <c r="I44" s="64"/>
-      <c r="J44" s="64"/>
+      <c r="J44" s="94" t="str">
+        <f>SUM(J36:J43)</f>
+        <v>0</v>
+      </c>
       <c r="K44" s="64"/>
       <c r="L44" s="64"/>
     </row>
     <row r="45" spans="1:14" customHeight="1" ht="18">
-      <c r="B45" s="64" t="s">
-        <v>57</v>
+      <c r="B45" s="64" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="true"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="14"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="false"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="14"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">No se emite comprobante por concepto de "PERCEPCIÓN, ANTI DUMPING, GESTIÓN DE COMPRA"</t>
+          </r>
+        </is>
       </c>
       <c r="C45" s="64"/>
       <c r="D45" s="64"/>
@@ -2472,8 +2527,57 @@
       <c r="L45" s="64"/>
     </row>
     <row r="46" spans="1:14" customHeight="1" ht="18">
-      <c r="B46" s="64" t="s">
-        <v>58</v>
+      <c r="B46" s="64" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="true"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="14"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="false"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="14"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">A nosotros se nos pagan los </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="true"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="14"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">Gastos Logísticos + Impuestos</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="false"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="14"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve"> una semana antes de que el contenedor</t>
+          </r>
+        </is>
       </c>
       <c r="C46" s="64"/>
       <c r="D46" s="64"/>
@@ -2488,7 +2592,7 @@
     </row>
     <row r="47" spans="1:14" customHeight="1" ht="18">
       <c r="B47" s="64" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C47" s="64"/>
       <c r="D47" s="64"/>
@@ -2501,101 +2605,126 @@
       <c r="K47" s="64"/>
       <c r="L47" s="64"/>
     </row>
-    <row r="48" spans="1:14">
-      <c r="B48" s="7"/>
-      <c r="C48" s="7"/>
-      <c r="D48" s="7"/>
-      <c r="E48" s="7"/>
-      <c r="F48" s="7"/>
-      <c r="G48" s="7"/>
-      <c r="H48" s="7"/>
-      <c r="I48" s="7"/>
-      <c r="J48" s="7"/>
-      <c r="K48" s="7"/>
-      <c r="L48" s="7"/>
-    </row>
-    <row r="49" spans="1:14" customHeight="1" ht="9">
-      <c r="B49" s="38"/>
-      <c r="C49" s="38"/>
-      <c r="E49" s="38"/>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38"/>
-      <c r="I49" s="38"/>
-      <c r="J49" s="38"/>
-      <c r="K49" s="38"/>
-      <c r="L49" s="38"/>
-      <c r="M49" s="38"/>
-    </row>
-    <row r="50" spans="1:14" customHeight="1" ht="31.8">
+    <row r="48" spans="1:14" customHeight="1" ht="18">
+      <c r="B48" s="64" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="true"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="14"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">*</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="false"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="14"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">El tipo de cambio referencial usado para la conversión a soles es del 3.70</t>
+          </r>
+        </is>
+      </c>
+      <c r="C48" s="64"/>
+      <c r="D48" s="64"/>
+      <c r="E48" s="64"/>
+      <c r="F48" s="64"/>
+      <c r="G48" s="64"/>
+      <c r="H48" s="64"/>
+      <c r="I48" s="64"/>
+      <c r="J48" s="64"/>
+      <c r="K48" s="64"/>
+      <c r="L48" s="64"/>
+    </row>
+    <row r="49" spans="1:14">
+      <c r="B49" s="7"/>
+      <c r="C49" s="7"/>
+      <c r="D49" s="7"/>
+      <c r="E49" s="7"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="7"/>
+      <c r="H49" s="7"/>
+      <c r="I49" s="7"/>
+      <c r="J49" s="7"/>
+      <c r="K49" s="7"/>
+      <c r="L49" s="7"/>
+    </row>
+    <row r="50" spans="1:14" customHeight="1" ht="9">
       <c r="B50" s="38"/>
       <c r="C50" s="38"/>
-      <c r="D50" s="37" t="s">
-        <v>0</v>
-      </c>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37"/>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37"/>
-      <c r="I50" s="37"/>
-      <c r="J50" s="37"/>
-      <c r="K50" s="37"/>
-      <c r="L50" s="37"/>
-      <c r="M50" s="37"/>
-    </row>
-    <row r="51" spans="1:14" customHeight="1" ht="21">
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="38"/>
+      <c r="K50" s="38"/>
+      <c r="L50" s="38"/>
+      <c r="M50" s="38"/>
+    </row>
+    <row r="51" spans="1:14" customHeight="1" ht="31.8">
       <c r="B51" s="38"/>
       <c r="C51" s="38"/>
-      <c r="D51" s="53" t="s">
-        <v>60</v>
-      </c>
-      <c r="E51" s="53"/>
-      <c r="F51" s="53"/>
-      <c r="G51" s="53"/>
-      <c r="H51" s="53"/>
-      <c r="I51" s="53"/>
-    </row>
-    <row r="52" spans="1:14">
+      <c r="D51" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37"/>
+      <c r="I51" s="37"/>
+      <c r="J51" s="37"/>
+      <c r="K51" s="37"/>
+      <c r="L51" s="37"/>
+      <c r="M51" s="37"/>
+    </row>
+    <row r="52" spans="1:14" customHeight="1" ht="21">
       <c r="B52" s="38"/>
       <c r="C52" s="38"/>
+      <c r="D52" s="53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E52" s="53"/>
+      <c r="F52" s="53"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
     </row>
     <row r="53" spans="1:14">
       <c r="B53" s="38"/>
       <c r="C53" s="38"/>
     </row>
-    <row r="54" spans="1:14" customHeight="1" ht="21">
-      <c r="B54" s="70" t="s">
-        <v>61</v>
-      </c>
-      <c r="C54" s="70"/>
-      <c r="D54" s="70"/>
-      <c r="E54" s="70"/>
-      <c r="F54" s="70"/>
-      <c r="G54" s="70"/>
-      <c r="H54" s="70"/>
-      <c r="I54" s="70"/>
-      <c r="J54" s="70"/>
-      <c r="K54" s="70"/>
-      <c r="L54" s="70"/>
-    </row>
-    <row r="56" spans="1:14">
-      <c r="B56" s="71" t="s">
-        <v>62</v>
-      </c>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="71"/>
-      <c r="F56" s="71"/>
-      <c r="G56" s="71"/>
-      <c r="H56" s="71"/>
-      <c r="I56" s="71"/>
-      <c r="J56" s="71"/>
-      <c r="K56" s="71"/>
-      <c r="L56" s="71"/>
+    <row r="54" spans="1:14">
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+    </row>
+    <row r="55" spans="1:14" customHeight="1" ht="21">
+      <c r="B55" s="70" t="s">
+        <v>63</v>
+      </c>
+      <c r="C55" s="70"/>
+      <c r="D55" s="70"/>
+      <c r="E55" s="70"/>
+      <c r="F55" s="70"/>
+      <c r="G55" s="70"/>
+      <c r="H55" s="70"/>
+      <c r="I55" s="70"/>
+      <c r="J55" s="70"/>
+      <c r="K55" s="70"/>
+      <c r="L55" s="70"/>
     </row>
     <row r="57" spans="1:14">
       <c r="B57" s="71" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C57" s="71"/>
       <c r="D57" s="71"/>
@@ -2609,38 +2738,38 @@
       <c r="L57" s="71"/>
     </row>
     <row r="58" spans="1:14">
-      <c r="B58" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="C58" s="49"/>
-      <c r="D58" s="49"/>
-      <c r="E58" s="49"/>
-      <c r="F58" s="49"/>
-      <c r="G58" s="49"/>
-      <c r="H58" s="49"/>
-      <c r="I58" s="49"/>
-      <c r="J58" s="49"/>
-      <c r="K58" s="49"/>
-      <c r="L58" s="49"/>
+      <c r="B58" s="71" t="s">
+        <v>65</v>
+      </c>
+      <c r="C58" s="71"/>
+      <c r="D58" s="71"/>
+      <c r="E58" s="71"/>
+      <c r="F58" s="71"/>
+      <c r="G58" s="71"/>
+      <c r="H58" s="71"/>
+      <c r="I58" s="71"/>
+      <c r="J58" s="71"/>
+      <c r="K58" s="71"/>
+      <c r="L58" s="71"/>
     </row>
     <row r="59" spans="1:14">
-      <c r="B59" s="71" t="s">
-        <v>65</v>
-      </c>
-      <c r="C59" s="71"/>
-      <c r="D59" s="71"/>
-      <c r="E59" s="71"/>
-      <c r="F59" s="71"/>
-      <c r="G59" s="71"/>
-      <c r="H59" s="71"/>
-      <c r="I59" s="71"/>
-      <c r="J59" s="71"/>
-      <c r="K59" s="71"/>
-      <c r="L59" s="71"/>
+      <c r="B59" s="49" t="s">
+        <v>66</v>
+      </c>
+      <c r="C59" s="49"/>
+      <c r="D59" s="49"/>
+      <c r="E59" s="49"/>
+      <c r="F59" s="49"/>
+      <c r="G59" s="49"/>
+      <c r="H59" s="49"/>
+      <c r="I59" s="49"/>
+      <c r="J59" s="49"/>
+      <c r="K59" s="49"/>
+      <c r="L59" s="49"/>
     </row>
     <row r="60" spans="1:14">
       <c r="B60" s="71" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C60" s="71"/>
       <c r="D60" s="71"/>
@@ -2654,38 +2783,38 @@
       <c r="L60" s="71"/>
     </row>
     <row r="61" spans="1:14">
-      <c r="B61" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="C61" s="49"/>
-      <c r="D61" s="49"/>
-      <c r="E61" s="49"/>
-      <c r="F61" s="49"/>
-      <c r="G61" s="49"/>
-      <c r="H61" s="49"/>
-      <c r="I61" s="49"/>
-      <c r="J61" s="49"/>
-      <c r="K61" s="49"/>
-      <c r="L61" s="49"/>
+      <c r="B61" s="71" t="s">
+        <v>68</v>
+      </c>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="71"/>
+      <c r="F61" s="71"/>
+      <c r="G61" s="71"/>
+      <c r="H61" s="71"/>
+      <c r="I61" s="71"/>
+      <c r="J61" s="71"/>
+      <c r="K61" s="71"/>
+      <c r="L61" s="71"/>
     </row>
     <row r="62" spans="1:14">
-      <c r="B62" s="71" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="71"/>
-      <c r="D62" s="71"/>
-      <c r="E62" s="71"/>
-      <c r="F62" s="71"/>
-      <c r="G62" s="71"/>
-      <c r="H62" s="71"/>
-      <c r="I62" s="71"/>
-      <c r="J62" s="71"/>
-      <c r="K62" s="71"/>
-      <c r="L62" s="71"/>
+      <c r="B62" s="49" t="s">
+        <v>69</v>
+      </c>
+      <c r="C62" s="49"/>
+      <c r="D62" s="49"/>
+      <c r="E62" s="49"/>
+      <c r="F62" s="49"/>
+      <c r="G62" s="49"/>
+      <c r="H62" s="49"/>
+      <c r="I62" s="49"/>
+      <c r="J62" s="49"/>
+      <c r="K62" s="49"/>
+      <c r="L62" s="49"/>
     </row>
     <row r="63" spans="1:14">
       <c r="B63" s="71" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C63" s="71"/>
       <c r="D63" s="71"/>
@@ -2700,7 +2829,7 @@
     </row>
     <row r="64" spans="1:14">
       <c r="B64" s="71" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C64" s="71"/>
       <c r="D64" s="71"/>
@@ -2715,7 +2844,7 @@
     </row>
     <row r="65" spans="1:14">
       <c r="B65" s="71" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C65" s="71"/>
       <c r="D65" s="71"/>
@@ -2730,7 +2859,7 @@
     </row>
     <row r="66" spans="1:14">
       <c r="B66" s="71" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C66" s="71"/>
       <c r="D66" s="71"/>
@@ -2745,7 +2874,7 @@
     </row>
     <row r="67" spans="1:14">
       <c r="B67" s="71" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C67" s="71"/>
       <c r="D67" s="71"/>
@@ -2760,7 +2889,7 @@
     </row>
     <row r="68" spans="1:14">
       <c r="B68" s="71" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C68" s="71"/>
       <c r="D68" s="71"/>
@@ -2775,7 +2904,7 @@
     </row>
     <row r="69" spans="1:14">
       <c r="B69" s="71" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C69" s="71"/>
       <c r="D69" s="71"/>
@@ -2790,7 +2919,7 @@
     </row>
     <row r="70" spans="1:14">
       <c r="B70" s="71" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C70" s="71"/>
       <c r="D70" s="71"/>
@@ -2805,7 +2934,7 @@
     </row>
     <row r="71" spans="1:14">
       <c r="B71" s="71" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C71" s="71"/>
       <c r="D71" s="71"/>
@@ -2820,7 +2949,7 @@
     </row>
     <row r="72" spans="1:14">
       <c r="B72" s="71" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C72" s="71"/>
       <c r="D72" s="71"/>
@@ -2834,68 +2963,96 @@
       <c r="L72" s="71"/>
     </row>
     <row r="73" spans="1:14">
-      <c r="B73" s="67" t="s">
-        <v>79</v>
-      </c>
-      <c r="C73" s="67"/>
-      <c r="D73" s="67"/>
-      <c r="E73" s="67"/>
-      <c r="F73" s="67"/>
-      <c r="G73" s="67"/>
-      <c r="H73" s="67"/>
-      <c r="I73" s="67"/>
-      <c r="J73" s="67"/>
-      <c r="K73" s="67"/>
-      <c r="L73" s="67"/>
+      <c r="B73" s="71" t="inlineStr">
+        <is>
+          <r>
+            <t xml:space="preserve">13.</t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="false"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="7"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve"> </t>
+          </r>
+          <r>
+            <rPr>
+              <rFont val="Calibri Light"/>
+              <b val="false"/>
+              <i val="false"/>
+              <strike val="false"/>
+              <color rgb="FF000000"/>
+              <sz val="11"/>
+              <u val="none"/>
+            </rPr>
+            <t xml:space="preserve">Los documentos de importación deber ser entregados a tiempo, de lo contrario, el participante no tendrá opción</t>
+          </r>
+        </is>
+      </c>
+      <c r="C73" s="71"/>
+      <c r="D73" s="71"/>
+      <c r="E73" s="71"/>
+      <c r="F73" s="71"/>
+      <c r="G73" s="71"/>
+      <c r="H73" s="71"/>
+      <c r="I73" s="71"/>
+      <c r="J73" s="71"/>
+      <c r="K73" s="71"/>
+      <c r="L73" s="71"/>
     </row>
     <row r="74" spans="1:14">
-      <c r="B74" s="71" t="s">
-        <v>80</v>
-      </c>
-      <c r="C74" s="71"/>
-      <c r="D74" s="71"/>
-      <c r="E74" s="71"/>
-      <c r="F74" s="71"/>
-      <c r="G74" s="71"/>
-      <c r="H74" s="71"/>
-      <c r="I74" s="71"/>
-      <c r="J74" s="71"/>
-      <c r="K74" s="71"/>
-      <c r="L74" s="71"/>
+      <c r="B74" s="67" t="s">
+        <v>81</v>
+      </c>
+      <c r="C74" s="67"/>
+      <c r="D74" s="67"/>
+      <c r="E74" s="67"/>
+      <c r="F74" s="67"/>
+      <c r="G74" s="67"/>
+      <c r="H74" s="67"/>
+      <c r="I74" s="67"/>
+      <c r="J74" s="67"/>
+      <c r="K74" s="67"/>
+      <c r="L74" s="67"/>
     </row>
     <row r="75" spans="1:14">
-      <c r="B75" s="67" t="s">
-        <v>81</v>
-      </c>
-      <c r="C75" s="67"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="67"/>
-      <c r="F75" s="67"/>
-      <c r="G75" s="67"/>
-      <c r="H75" s="67"/>
-      <c r="I75" s="67"/>
-      <c r="J75" s="67"/>
-      <c r="K75" s="67"/>
-      <c r="L75" s="67"/>
+      <c r="B75" s="71" t="s">
+        <v>82</v>
+      </c>
+      <c r="C75" s="71"/>
+      <c r="D75" s="71"/>
+      <c r="E75" s="71"/>
+      <c r="F75" s="71"/>
+      <c r="G75" s="71"/>
+      <c r="H75" s="71"/>
+      <c r="I75" s="71"/>
+      <c r="J75" s="71"/>
+      <c r="K75" s="71"/>
+      <c r="L75" s="71"/>
     </row>
     <row r="76" spans="1:14">
-      <c r="B76" s="71" t="s">
-        <v>82</v>
-      </c>
-      <c r="C76" s="71"/>
-      <c r="D76" s="71"/>
-      <c r="E76" s="71"/>
-      <c r="F76" s="71"/>
-      <c r="G76" s="71"/>
-      <c r="H76" s="71"/>
-      <c r="I76" s="71"/>
-      <c r="J76" s="71"/>
-      <c r="K76" s="71"/>
-      <c r="L76" s="71"/>
+      <c r="B76" s="67" t="s">
+        <v>83</v>
+      </c>
+      <c r="C76" s="67"/>
+      <c r="D76" s="67"/>
+      <c r="E76" s="67"/>
+      <c r="F76" s="67"/>
+      <c r="G76" s="67"/>
+      <c r="H76" s="67"/>
+      <c r="I76" s="67"/>
+      <c r="J76" s="67"/>
+      <c r="K76" s="67"/>
+      <c r="L76" s="67"/>
     </row>
     <row r="77" spans="1:14">
       <c r="B77" s="71" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C77" s="71"/>
       <c r="D77" s="71"/>
@@ -2910,7 +3067,7 @@
     </row>
     <row r="78" spans="1:14">
       <c r="B78" s="71" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C78" s="71"/>
       <c r="D78" s="71"/>
@@ -2925,7 +3082,7 @@
     </row>
     <row r="79" spans="1:14">
       <c r="B79" s="71" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C79" s="71"/>
       <c r="D79" s="71"/>
@@ -2940,7 +3097,7 @@
     </row>
     <row r="80" spans="1:14">
       <c r="B80" s="71" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C80" s="71"/>
       <c r="D80" s="71"/>
@@ -2954,61 +3111,67 @@
       <c r="L80" s="71"/>
     </row>
     <row r="81" spans="1:14">
-      <c r="A81" s="32"/>
-      <c r="B81" s="72" t="s">
-        <v>87</v>
-      </c>
-      <c r="C81" s="72"/>
-      <c r="D81" s="72"/>
-      <c r="E81" s="72"/>
-      <c r="F81" s="72"/>
-      <c r="G81" s="72"/>
-      <c r="H81" s="72"/>
-      <c r="I81" s="72"/>
-      <c r="J81" s="72"/>
-      <c r="K81" s="72"/>
-      <c r="L81" s="72"/>
+      <c r="B81" s="71" t="s">
+        <v>88</v>
+      </c>
+      <c r="C81" s="71"/>
+      <c r="D81" s="71"/>
+      <c r="E81" s="71"/>
+      <c r="F81" s="71"/>
+      <c r="G81" s="71"/>
+      <c r="H81" s="71"/>
+      <c r="I81" s="71"/>
+      <c r="J81" s="71"/>
+      <c r="K81" s="71"/>
+      <c r="L81" s="71"/>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="32"/>
-      <c r="B82" s="71" t="s">
-        <v>88</v>
-      </c>
-      <c r="C82" s="71"/>
-      <c r="D82" s="71"/>
-      <c r="E82" s="71"/>
-      <c r="F82" s="71"/>
-      <c r="G82" s="71"/>
-      <c r="H82" s="71"/>
-      <c r="I82" s="71"/>
-      <c r="J82" s="71"/>
-      <c r="K82" s="71"/>
-      <c r="L82" s="71"/>
+      <c r="B82" s="72" t="s">
+        <v>89</v>
+      </c>
+      <c r="C82" s="72"/>
+      <c r="D82" s="72"/>
+      <c r="E82" s="72"/>
+      <c r="F82" s="72"/>
+      <c r="G82" s="72"/>
+      <c r="H82" s="72"/>
+      <c r="I82" s="72"/>
+      <c r="J82" s="72"/>
+      <c r="K82" s="72"/>
+      <c r="L82" s="72"/>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="32"/>
-      <c r="B83" s="72" t="s">
-        <v>89</v>
-      </c>
-      <c r="C83" s="72"/>
-      <c r="D83" s="72"/>
-      <c r="E83" s="72"/>
-      <c r="F83" s="72"/>
-      <c r="G83" s="72"/>
-      <c r="H83" s="72"/>
-      <c r="I83" s="72"/>
-      <c r="J83" s="72"/>
-      <c r="K83" s="72"/>
-      <c r="L83" s="72"/>
-    </row>
-    <row r="85" spans="1:14">
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="38"/>
-      <c r="F85" s="38"/>
-      <c r="G85" s="38"/>
-      <c r="H85" s="38"/>
-      <c r="I85" s="38"/>
+      <c r="B83" s="71" t="s">
+        <v>90</v>
+      </c>
+      <c r="C83" s="71"/>
+      <c r="D83" s="71"/>
+      <c r="E83" s="71"/>
+      <c r="F83" s="71"/>
+      <c r="G83" s="71"/>
+      <c r="H83" s="71"/>
+      <c r="I83" s="71"/>
+      <c r="J83" s="71"/>
+      <c r="K83" s="71"/>
+      <c r="L83" s="71"/>
+    </row>
+    <row r="84" spans="1:14">
+      <c r="A84" s="32"/>
+      <c r="B84" s="72" t="s">
+        <v>91</v>
+      </c>
+      <c r="C84" s="72"/>
+      <c r="D84" s="72"/>
+      <c r="E84" s="72"/>
+      <c r="F84" s="72"/>
+      <c r="G84" s="72"/>
+      <c r="H84" s="72"/>
+      <c r="I84" s="72"/>
+      <c r="J84" s="72"/>
+      <c r="K84" s="72"/>
+      <c r="L84" s="72"/>
     </row>
     <row r="86" spans="1:14">
       <c r="C86" s="38"/>
@@ -3064,7 +3227,7 @@
       <c r="H91" s="38"/>
       <c r="I91" s="38"/>
     </row>
-    <row r="92" spans="1:14" customHeight="1" ht="15.6">
+    <row r="92" spans="1:14">
       <c r="C92" s="38"/>
       <c r="D92" s="38"/>
       <c r="E92" s="38"/>
@@ -3082,7 +3245,7 @@
       <c r="H93" s="38"/>
       <c r="I93" s="38"/>
     </row>
-    <row r="94" spans="1:14">
+    <row r="94" spans="1:14" customHeight="1" ht="15.6">
       <c r="C94" s="38"/>
       <c r="D94" s="38"/>
       <c r="E94" s="38"/>
@@ -3091,51 +3254,59 @@
       <c r="H94" s="38"/>
       <c r="I94" s="38"/>
     </row>
-    <row r="100" spans="1:14" customHeight="1" ht="15.6"/>
+    <row r="95" spans="1:14">
+      <c r="C95" s="38"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="38"/>
+      <c r="F95" s="38"/>
+      <c r="G95" s="38"/>
+      <c r="H95" s="38"/>
+      <c r="I95" s="38"/>
+    </row>
+    <row r="101" spans="1:14" customHeight="1" ht="15.6"/>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="true" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
   <mergeCells>
-    <mergeCell ref="B73:L73"/>
     <mergeCell ref="B74:L74"/>
+    <mergeCell ref="B75:L75"/>
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="I7:L7"/>
-    <mergeCell ref="B58:L58"/>
-    <mergeCell ref="B47:L47"/>
+    <mergeCell ref="B59:L59"/>
+    <mergeCell ref="B48:L48"/>
     <mergeCell ref="C38:E38"/>
     <mergeCell ref="K38:L38"/>
-    <mergeCell ref="B43:L43"/>
-    <mergeCell ref="B56:L56"/>
-    <mergeCell ref="B69:L69"/>
     <mergeCell ref="B57:L57"/>
+    <mergeCell ref="B70:L70"/>
+    <mergeCell ref="B58:L58"/>
     <mergeCell ref="G37:H37"/>
     <mergeCell ref="J11:L11"/>
-    <mergeCell ref="B83:L83"/>
-    <mergeCell ref="B66:L66"/>
+    <mergeCell ref="B84:L84"/>
     <mergeCell ref="B67:L67"/>
     <mergeCell ref="B68:L68"/>
-    <mergeCell ref="B59:L59"/>
+    <mergeCell ref="B69:L69"/>
     <mergeCell ref="B60:L60"/>
     <mergeCell ref="B61:L61"/>
     <mergeCell ref="B62:L62"/>
     <mergeCell ref="B63:L63"/>
     <mergeCell ref="B64:L64"/>
     <mergeCell ref="B65:L65"/>
-    <mergeCell ref="B70:L70"/>
+    <mergeCell ref="B66:L66"/>
     <mergeCell ref="B71:L71"/>
     <mergeCell ref="B72:L72"/>
+    <mergeCell ref="B73:L73"/>
+    <mergeCell ref="B83:L83"/>
     <mergeCell ref="B82:L82"/>
     <mergeCell ref="B81:L81"/>
-    <mergeCell ref="B80:L80"/>
-    <mergeCell ref="B75:L75"/>
     <mergeCell ref="B76:L76"/>
     <mergeCell ref="B77:L77"/>
     <mergeCell ref="B78:L78"/>
     <mergeCell ref="B79:L79"/>
-    <mergeCell ref="B49:C53"/>
+    <mergeCell ref="B80:L80"/>
+    <mergeCell ref="B50:C54"/>
     <mergeCell ref="B19:F19"/>
     <mergeCell ref="C35:E35"/>
-    <mergeCell ref="B54:L54"/>
-    <mergeCell ref="B45:L45"/>
+    <mergeCell ref="B55:L55"/>
+    <mergeCell ref="B46:L46"/>
     <mergeCell ref="G38:H38"/>
     <mergeCell ref="K37:L37"/>
     <mergeCell ref="C37:E37"/>
@@ -3144,7 +3315,7 @@
     <mergeCell ref="B20:I20"/>
     <mergeCell ref="B21:I21"/>
     <mergeCell ref="B22:I22"/>
-    <mergeCell ref="D50:J50"/>
+    <mergeCell ref="D51:J51"/>
     <mergeCell ref="B31:J31"/>
     <mergeCell ref="B26:I26"/>
     <mergeCell ref="B12:L12"/>
@@ -3152,10 +3323,10 @@
     <mergeCell ref="B14:J14"/>
     <mergeCell ref="B16:J16"/>
     <mergeCell ref="B15:J15"/>
-    <mergeCell ref="C85:I94"/>
+    <mergeCell ref="C86:I95"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="E2:L2"/>
-    <mergeCell ref="D51:I51"/>
+    <mergeCell ref="D52:I52"/>
     <mergeCell ref="E3:J3"/>
     <mergeCell ref="E4:J4"/>
     <mergeCell ref="K36:L36"/>
@@ -3165,11 +3336,11 @@
     <mergeCell ref="B34:L34"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="J10:L10"/>
-    <mergeCell ref="B46:L46"/>
-    <mergeCell ref="B44:L44"/>
+    <mergeCell ref="B47:L47"/>
+    <mergeCell ref="B45:L45"/>
     <mergeCell ref="F11:G11"/>
-    <mergeCell ref="K50:M50"/>
-    <mergeCell ref="E49:M49"/>
+    <mergeCell ref="K51:M51"/>
+    <mergeCell ref="E50:M50"/>
     <mergeCell ref="J9:L9"/>
     <mergeCell ref="B2:C6"/>
     <mergeCell ref="E7:G7"/>
@@ -3193,6 +3364,13 @@
     <mergeCell ref="C41:E41"/>
     <mergeCell ref="G41:H41"/>
     <mergeCell ref="K41:L41"/>
+    <mergeCell ref="C42:E42"/>
+    <mergeCell ref="G42:H42"/>
+    <mergeCell ref="K42:L42"/>
+    <mergeCell ref="C43:E43"/>
+    <mergeCell ref="G43:H43"/>
+    <mergeCell ref="K43:L43"/>
+    <mergeCell ref="B44:E44"/>
     <mergeCell ref="C8:C9"/>
   </mergeCells>
   <dataValidations count="5">
@@ -3224,7 +3402,7 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="48" man="1"/>
+    <brk id="49" man="1"/>
   </rowBreaks>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3235,22 +3413,24 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:O47"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="2" max="2" width="24.708252" bestFit="true" customWidth="true" style="0"/>
-    <col min="3" max="3" width="37.705078" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="22.280273" bestFit="true" customWidth="true" style="0"/>
-    <col min="5" max="5" width="30.563965" bestFit="true" customWidth="true" style="0"/>
-    <col min="6" max="6" width="21.137695" bestFit="true" customWidth="true" style="0"/>
-    <col min="7" max="7" width="31.706543" bestFit="true" customWidth="true" style="0"/>
-    <col min="8" max="8" width="31.706543" bestFit="true" customWidth="true" style="0"/>
-    <col min="9" max="9" width="12.854004" bestFit="true" customWidth="true" style="0"/>
+    <col min="3" max="3" width="32.991943" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="34.134521" bestFit="true" customWidth="true" style="0"/>
+    <col min="5" max="5" width="31.706543" bestFit="true" customWidth="true" style="0"/>
+    <col min="6" max="6" width="35.2771" bestFit="true" customWidth="true" style="0"/>
+    <col min="7" max="7" width="28.135986" bestFit="true" customWidth="true" style="0"/>
+    <col min="8" max="8" width="21.137695" bestFit="true" customWidth="true" style="0"/>
+    <col min="9" max="9" width="38.847656" bestFit="true" customWidth="true" style="0"/>
+    <col min="10" max="10" width="37.705078" bestFit="true" customWidth="true" style="0"/>
+    <col min="11" max="11" width="12.854004" bestFit="true" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:15">
       <c r="B3" s="75" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C3" s="74"/>
       <c r="D3" s="74"/>
@@ -3258,35 +3438,41 @@
       <c r="F3" s="74"/>
       <c r="G3" s="74"/>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:15">
       <c r="B5" s="78" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C5" s="80" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D5" s="80" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E5" s="80" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F5" s="80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G5" s="80" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H5" s="80" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I5" s="80" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>56</v>
+      </c>
+      <c r="J5" s="80" t="s">
+        <v>57</v>
+      </c>
+      <c r="K5" s="80" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15">
       <c r="B6" s="74" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C6" s="74">
         <v>0</v>
@@ -3306,19 +3492,25 @@
       <c r="H6" s="74">
         <v>0</v>
       </c>
-      <c r="I6" s="82">
-        <v>0</v>
-      </c>
-      <c r="L6" s="76" t="s">
-        <v>94</v>
-      </c>
-      <c r="M6" s="76" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+      <c r="I6" s="74">
+        <v>0</v>
+      </c>
+      <c r="J6" s="74">
+        <v>0</v>
+      </c>
+      <c r="K6" s="82">
+        <v>100</v>
+      </c>
+      <c r="N6" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="O6" s="76" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15">
       <c r="B7" s="74" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" s="74">
         <v>0</v>
@@ -3338,41 +3530,55 @@
       <c r="H7" s="74">
         <v>0</v>
       </c>
-      <c r="I7" s="83">
-        <v>0.1</v>
-      </c>
-      <c r="L7" s="77" t="s">
-        <v>18</v>
-      </c>
-      <c r="M7" s="77"/>
-    </row>
-    <row r="8" spans="1:13">
+      <c r="I7" s="74">
+        <v>0</v>
+      </c>
+      <c r="J7" s="74">
+        <v>0</v>
+      </c>
+      <c r="K7" s="83">
+        <v>1.55</v>
+      </c>
+      <c r="N7" s="77" t="s">
+        <v>19</v>
+      </c>
+      <c r="O7" s="77">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
       <c r="B8" s="74" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C8" s="81">
-        <v>1.95</v>
+        <v>1.8</v>
       </c>
       <c r="D8" s="81">
-        <v>2.2386471408647</v>
+        <v>1.55</v>
       </c>
       <c r="E8" s="81">
-        <v>1.6</v>
+        <v>2.05</v>
       </c>
       <c r="F8" s="81">
-        <v>1.2</v>
+        <v>1.65</v>
       </c>
       <c r="G8" s="81">
-        <v>2.92</v>
+        <v>2.2</v>
       </c>
       <c r="H8" s="81">
-        <v>1.2</v>
-      </c>
-      <c r="I8" s="74"/>
-    </row>
-    <row r="9" spans="1:13">
+        <v>1.65</v>
+      </c>
+      <c r="I8" s="81">
+        <v>1.334375</v>
+      </c>
+      <c r="J8" s="81">
+        <v>1.54</v>
+      </c>
+      <c r="K8" s="74"/>
+    </row>
+    <row r="9" spans="1:15">
       <c r="B9" s="79" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C9" s="81">
         <v>0</v>
@@ -3392,38 +3598,50 @@
       <c r="H9" s="81">
         <v>0</v>
       </c>
-      <c r="I9" s="74"/>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="I9" s="81">
+        <v>0</v>
+      </c>
+      <c r="J9" s="81">
+        <v>0</v>
+      </c>
+      <c r="K9" s="74"/>
+    </row>
+    <row r="10" spans="1:15">
       <c r="B10" s="74" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C10" s="74">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D10" s="74">
-        <v>717</v>
+        <v>390</v>
       </c>
       <c r="E10" s="74">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="F10" s="74">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="G10" s="74">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H10" s="74">
-        <v>86</v>
-      </c>
-      <c r="I10" s="74" t="str">
-        <f>SUM(C10:H10)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>275</v>
+      </c>
+      <c r="I10" s="74">
+        <v>520</v>
+      </c>
+      <c r="J10" s="74">
+        <v>140</v>
+      </c>
+      <c r="K10" s="74" t="str">
+        <f>SUM(C10:J10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
       <c r="B11" s="74" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C11" s="81" t="str">
         <f>C8*C10</f>
@@ -3449,14 +3667,22 @@
         <f>H8*H10</f>
         <v>0</v>
       </c>
-      <c r="I11" s="86" t="str">
-        <f>SUM(C11:H11)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="I11" s="81" t="str">
+        <f>I8*I10</f>
+        <v>0</v>
+      </c>
+      <c r="J11" s="81" t="str">
+        <f>J8*J10</f>
+        <v>0</v>
+      </c>
+      <c r="K11" s="86" t="str">
+        <f>SUM(C11:J11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
       <c r="B12" s="79" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C12" s="81" t="str">
         <f>C10*C9</f>
@@ -3482,250 +3708,314 @@
         <f>H10*H9</f>
         <v>0</v>
       </c>
-      <c r="I12" s="86" t="str">
-        <f>SUM(C12:H12)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="I12" s="81" t="str">
+        <f>I10*I9</f>
+        <v>0</v>
+      </c>
+      <c r="J12" s="81" t="str">
+        <f>J10*J9</f>
+        <v>0</v>
+      </c>
+      <c r="K12" s="86" t="str">
+        <f>SUM(C12:J12)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
       <c r="B13" s="74" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C13" s="84" t="str">
-        <f>C11/I11</f>
+        <f>C11/K11</f>
         <v>0</v>
       </c>
       <c r="D13" s="84" t="str">
-        <f>D11/I11</f>
+        <f>D11/K11</f>
         <v>0</v>
       </c>
       <c r="E13" s="84" t="str">
-        <f>E11/I11</f>
+        <f>E11/K11</f>
         <v>0</v>
       </c>
       <c r="F13" s="84" t="str">
-        <f>F11/I11</f>
+        <f>F11/K11</f>
         <v>0</v>
       </c>
       <c r="G13" s="84" t="str">
-        <f>G11/I11</f>
+        <f>G11/K11</f>
         <v>0</v>
       </c>
       <c r="H13" s="84" t="str">
-        <f>H11/I11</f>
-        <v>0</v>
-      </c>
-      <c r="I13" s="74"/>
-    </row>
-    <row r="14" spans="1:13">
+        <f>H11/K11</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="84" t="str">
+        <f>I11/K11</f>
+        <v>0</v>
+      </c>
+      <c r="J13" s="84" t="str">
+        <f>J11/K11</f>
+        <v>0</v>
+      </c>
+      <c r="K13" s="74"/>
+    </row>
+    <row r="14" spans="1:15">
       <c r="B14" s="74" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C14" s="81" t="str">
-        <f>ROUNDUP(I14*C13,2)</f>
+        <f>K14*C13</f>
         <v>0</v>
       </c>
       <c r="D14" s="81" t="str">
-        <f>ROUNDUP(I14*D13,2)</f>
+        <f>K14*D13</f>
         <v>0</v>
       </c>
       <c r="E14" s="81" t="str">
-        <f>ROUNDUP(I14*E13,2)</f>
+        <f>K14*E13</f>
         <v>0</v>
       </c>
       <c r="F14" s="81" t="str">
-        <f>ROUNDUP(I14*F13,2)</f>
+        <f>K14*F13</f>
         <v>0</v>
       </c>
       <c r="G14" s="81" t="str">
-        <f>ROUNDUP(I14*G13,2)</f>
+        <f>K14*G13</f>
         <v>0</v>
       </c>
       <c r="H14" s="81" t="str">
-        <f>ROUNDUP(I14*H13,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I14" s="86" t="str">
-        <f>IF(I7&lt;1, ROUNDUP(M7*0.6, 0), ROUNDUP(M7*0.6*I7, 0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <f>K14*H13</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="81" t="str">
+        <f>K14*I13</f>
+        <v>0</v>
+      </c>
+      <c r="J14" s="81" t="str">
+        <f>K14*J13</f>
+        <v>0</v>
+      </c>
+      <c r="K14" s="86" t="str">
+        <f>IF(K7&lt;1, O7*0.6, O7*0.6*K7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
       <c r="B15" s="74" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C15" s="81" t="str">
-        <f>ROUNDUP(C11+C14,2)</f>
+        <f>C11+C14</f>
         <v>0</v>
       </c>
       <c r="D15" s="81" t="str">
-        <f>ROUNDUP(D11+D14,2)</f>
+        <f>D11+D14</f>
         <v>0</v>
       </c>
       <c r="E15" s="81" t="str">
-        <f>ROUNDUP(E11+E14,2)</f>
+        <f>E11+E14</f>
         <v>0</v>
       </c>
       <c r="F15" s="81" t="str">
-        <f>ROUNDUP(F11+F14,2)</f>
+        <f>F11+F14</f>
         <v>0</v>
       </c>
       <c r="G15" s="81" t="str">
-        <f>ROUNDUP(G11+G14,2)</f>
+        <f>G11+G14</f>
         <v>0</v>
       </c>
       <c r="H15" s="81" t="str">
-        <f>ROUNDUP(H11+H14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I15" s="86" t="str">
-        <f>SUM(C15:H15)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <f>H11+H14</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="81" t="str">
+        <f>I11+I14</f>
+        <v>0</v>
+      </c>
+      <c r="J15" s="81" t="str">
+        <f>J11+J14</f>
+        <v>0</v>
+      </c>
+      <c r="K15" s="86" t="str">
+        <f>SUM(C15:J15)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
       <c r="B16" s="79" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C16" s="81" t="str">
-        <f>ROUNDUP(C12+C14,2)</f>
+        <f>C12+C14</f>
         <v>0</v>
       </c>
       <c r="D16" s="81" t="str">
-        <f>ROUNDUP(D12+D14,2)</f>
+        <f>D12+D14</f>
         <v>0</v>
       </c>
       <c r="E16" s="81" t="str">
-        <f>ROUNDUP(E12+E14,2)</f>
+        <f>E12+E14</f>
         <v>0</v>
       </c>
       <c r="F16" s="81" t="str">
-        <f>ROUNDUP(F12+F14,2)</f>
+        <f>F12+F14</f>
         <v>0</v>
       </c>
       <c r="G16" s="81" t="str">
-        <f>ROUNDUP(G12+G14,2)</f>
+        <f>G12+G14</f>
         <v>0</v>
       </c>
       <c r="H16" s="81" t="str">
-        <f>ROUNDUP(H12+H14,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I16" s="86" t="str">
-        <f>SUM(C16:H16)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <f>H12+H14</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="81" t="str">
+        <f>I12+I14</f>
+        <v>0</v>
+      </c>
+      <c r="J16" s="81" t="str">
+        <f>J12+J14</f>
+        <v>0</v>
+      </c>
+      <c r="K16" s="86" t="str">
+        <f>SUM(C16:J16)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
       <c r="B17" s="74" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C17" s="81" t="str">
-        <f>IF(I15&gt;5000,ROUND(100*C13,2),ROUND(50*C13,2))</f>
+        <f>IF(K11&gt;5000,100*C13,50*C13)</f>
         <v>0</v>
       </c>
       <c r="D17" s="81" t="str">
-        <f>IF(I15&gt;5000,ROUND(100*D13,2),ROUND(50*D13,2))</f>
+        <f>IF(K11&gt;5000,100*D13,50*D13)</f>
         <v>0</v>
       </c>
       <c r="E17" s="81" t="str">
-        <f>IF(I15&gt;5000,ROUND(100*E13,2),ROUND(50*E13,2))</f>
+        <f>IF(K11&gt;5000,100*E13,50*E13)</f>
         <v>0</v>
       </c>
       <c r="F17" s="81" t="str">
-        <f>IF(I15&gt;5000,ROUND(100*F13,2),ROUND(50*F13,2))</f>
+        <f>IF(K11&gt;5000,100*F13,50*F13)</f>
         <v>0</v>
       </c>
       <c r="G17" s="81" t="str">
-        <f>IF(I15&gt;5000,ROUND(100*G13,2),ROUND(50*G13,2))</f>
+        <f>IF(K11&gt;5000,100*G13,50*G13)</f>
         <v>0</v>
       </c>
       <c r="H17" s="81" t="str">
-        <f>IF(I15&gt;5000,ROUND(100*H13,2),ROUND(50*H13,2))</f>
-        <v>0</v>
-      </c>
-      <c r="I17" s="86" t="str">
-        <f>SUM(C17:H17)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <f>IF(K11&gt;5000,100*H13,50*H13)</f>
+        <v>0</v>
+      </c>
+      <c r="I17" s="81" t="str">
+        <f>IF(K11&gt;5000,100*I13,50*I13)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="81" t="str">
+        <f>IF(K11&gt;5000,100*J13,50*J13)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="86" t="str">
+        <f>SUM(C17:J17)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15">
       <c r="B18" s="74" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C18" s="81" t="str">
-        <f>ROUNDUP(C15+C17,2)</f>
+        <f>C15+C17</f>
         <v>0</v>
       </c>
       <c r="D18" s="81" t="str">
-        <f>ROUNDUP(D15+D17,2)</f>
+        <f>D15+D17</f>
         <v>0</v>
       </c>
       <c r="E18" s="81" t="str">
-        <f>ROUNDUP(E15+E17,2)</f>
+        <f>E15+E17</f>
         <v>0</v>
       </c>
       <c r="F18" s="81" t="str">
-        <f>ROUNDUP(F15+F17,2)</f>
+        <f>F15+F17</f>
         <v>0</v>
       </c>
       <c r="G18" s="81" t="str">
-        <f>ROUNDUP(G15+G17,2)</f>
+        <f>G15+G17</f>
         <v>0</v>
       </c>
       <c r="H18" s="81" t="str">
-        <f>ROUNDUP(H15+H17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I18" s="86" t="str">
-        <f>SUM(C18:H18)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <f>H15+H17</f>
+        <v>0</v>
+      </c>
+      <c r="I18" s="81" t="str">
+        <f>I15+I17</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="81" t="str">
+        <f>J15+J17</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="86" t="str">
+        <f>SUM(C18:J18)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15">
       <c r="B19" s="79" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C19" s="81" t="str">
-        <f>ROUNDUP(C16+C17,2)</f>
+        <f>C16+C17</f>
         <v>0</v>
       </c>
       <c r="D19" s="81" t="str">
-        <f>ROUNDUP(D16+D17,2)</f>
+        <f>D16+D17</f>
         <v>0</v>
       </c>
       <c r="E19" s="81" t="str">
-        <f>ROUNDUP(E16+E17,2)</f>
+        <f>E16+E17</f>
         <v>0</v>
       </c>
       <c r="F19" s="81" t="str">
-        <f>ROUNDUP(F16+F17,2)</f>
+        <f>F16+F17</f>
         <v>0</v>
       </c>
       <c r="G19" s="81" t="str">
-        <f>ROUNDUP(G16+G17,2)</f>
+        <f>G16+G17</f>
         <v>0</v>
       </c>
       <c r="H19" s="81" t="str">
-        <f>ROUNDUP(H16+H17,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I19" s="86" t="str">
-        <f>SUM(C19:H19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <f>H16+H17</f>
+        <v>0</v>
+      </c>
+      <c r="I19" s="81" t="str">
+        <f>I16+I17</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="81" t="str">
+        <f>J16+J17</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="86" t="str">
+        <f>SUM(C19:J19)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15">
       <c r="B23" s="75" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C23" s="74"/>
       <c r="D23" s="74"/>
       <c r="E23" s="74"/>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:15">
       <c r="B26" s="74" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C26" s="81">
         <v>0</v>
@@ -3745,12 +4035,18 @@
       <c r="H26" s="81">
         <v>0</v>
       </c>
-      <c r="I26" s="81" t="str">
-        <f>SUM(C26:H26)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="I26" s="81">
+        <v>0</v>
+      </c>
+      <c r="J26" s="81">
+        <v>0</v>
+      </c>
+      <c r="K26" s="81" t="str">
+        <f>SUM(C26:J26)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15">
       <c r="C27" s="87">
         <v>0</v>
       </c>
@@ -3769,14 +4065,20 @@
       <c r="H27" s="87">
         <v>0</v>
       </c>
-      <c r="I27" s="84" t="str">
-        <f>SUM(C27:H27)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+      <c r="I27" s="87">
+        <v>0</v>
+      </c>
+      <c r="J27" s="87">
+        <v>0</v>
+      </c>
+      <c r="K27" s="84" t="str">
+        <f>SUM(C27:J27)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15">
       <c r="B28" s="74" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C28" s="81" t="str">
         <f>MAX(C19,C18)*C27</f>
@@ -3803,13 +4105,21 @@
         <v>0</v>
       </c>
       <c r="I28" s="81" t="str">
-        <f>SUM(C28:H28)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <f>MAX(I19,I18)*I27</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="81" t="str">
+        <f>MAX(J19,J18)*J27</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="81" t="str">
+        <f>SUM(C28:J28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15">
       <c r="B29" s="74" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C29" s="81" t="str">
         <f>0.16*(MAX(C19,C18)+C28)</f>
@@ -3836,13 +4146,21 @@
         <v>0</v>
       </c>
       <c r="I29" s="81" t="str">
-        <f>SUM(C29:H29)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <f>0.16*(MAX(I19,I18)+I28)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="81" t="str">
+        <f>0.16*(MAX(J19,J18)+J28)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="81" t="str">
+        <f>SUM(C29:J29)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15">
       <c r="B30" s="74" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C30" s="81" t="str">
         <f>0.02*(MAX(C19,C18)+C28)</f>
@@ -3869,13 +4187,21 @@
         <v>0</v>
       </c>
       <c r="I30" s="81" t="str">
-        <f>SUM(C30:H30)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <f>0.02*(MAX(I19,I18)+I28)</f>
+        <v>0</v>
+      </c>
+      <c r="J30" s="81" t="str">
+        <f>0.02*(MAX(J19,J18)+J28)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="81" t="str">
+        <f>SUM(C30:J30)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15">
       <c r="B31" s="74" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C31" s="81" t="str">
         <f>0.035*(MAX(C18,C19) +C28+C29+C30)</f>
@@ -3902,13 +4228,21 @@
         <v>0</v>
       </c>
       <c r="I31" s="81" t="str">
-        <f>SUM(C31:H31)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <f>0.035*(MAX(I18,I19) +I28+I29+I30)</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="81" t="str">
+        <f>0.035*(MAX(J18,J19) +J28+J29+J30)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="81" t="str">
+        <f>SUM(C31:J31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15">
       <c r="B32" s="74" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C32" s="81" t="str">
         <f>SUM(C28:C31)</f>
@@ -3938,193 +4272,245 @@
         <f>SUM(I28:I31)</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:13">
+      <c r="J32" s="81" t="str">
+        <f>SUM(J28:J31)</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="81" t="str">
+        <f>SUM(K28:K31)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15">
       <c r="B37" s="75" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C37" s="74"/>
       <c r="D37" s="74"/>
       <c r="E37" s="74"/>
     </row>
-    <row r="40" spans="1:13">
+    <row r="40" spans="1:15">
       <c r="B40" s="74" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C40" s="81" t="str">
-        <f>C13*I40</f>
+        <f>C13*K40</f>
         <v>0</v>
       </c>
       <c r="D40" s="81" t="str">
-        <f>D13*I40</f>
+        <f>D13*K40</f>
         <v>0</v>
       </c>
       <c r="E40" s="81" t="str">
-        <f>E13*I40</f>
+        <f>E13*K40</f>
         <v>0</v>
       </c>
       <c r="F40" s="81" t="str">
-        <f>F13*I40</f>
+        <f>F13*K40</f>
         <v>0</v>
       </c>
       <c r="G40" s="81" t="str">
-        <f>G13*I40</f>
+        <f>G13*K40</f>
         <v>0</v>
       </c>
       <c r="H40" s="81" t="str">
-        <f>H13*I40</f>
+        <f>H13*K40</f>
         <v>0</v>
       </c>
       <c r="I40" s="81" t="str">
-        <f>IF(I7&lt;1, ROUNDUP(M7*0.4, 0), ROUNDUP(M7*0.4*I7, 0))</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13">
+        <f>I13*K40</f>
+        <v>0</v>
+      </c>
+      <c r="J40" s="81" t="str">
+        <f>J13*K40</f>
+        <v>0</v>
+      </c>
+      <c r="K40" s="81" t="str">
+        <f>IF(K7&lt;1, O7*0.4,O7*0.4*K7)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:15">
       <c r="B41"/>
     </row>
-    <row r="43" spans="1:13">
+    <row r="43" spans="1:15">
       <c r="B43" s="74" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="C43" s="74" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D43" s="74" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E43" s="74" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F43" s="74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G43" s="74" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="H43" s="74" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="I43" s="74" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+        <v>56</v>
+      </c>
+      <c r="J43" s="74" t="s">
+        <v>57</v>
+      </c>
+      <c r="K43" s="74" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="44" spans="1:15">
       <c r="B44" s="74" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C44" s="81" t="str">
-        <f>SUM(C15,C40,C32,(C26*C10))</f>
+        <f>SUM(C15,C40,C32,(C26))</f>
         <v>0</v>
       </c>
       <c r="D44" s="81" t="str">
-        <f>SUM(D15,D40,D32,(D26*D10))</f>
+        <f>SUM(D15,D40,D32,(D26))</f>
         <v>0</v>
       </c>
       <c r="E44" s="81" t="str">
-        <f>SUM(E15,E40,E32,(E26*E10))</f>
+        <f>SUM(E15,E40,E32,(E26))</f>
         <v>0</v>
       </c>
       <c r="F44" s="81" t="str">
-        <f>SUM(F15,F40,F32,(F26*F10))</f>
+        <f>SUM(F15,F40,F32,(F26))</f>
         <v>0</v>
       </c>
       <c r="G44" s="81" t="str">
-        <f>SUM(G15,G40,G32,(G26*G10))</f>
+        <f>SUM(G15,G40,G32,(G26))</f>
         <v>0</v>
       </c>
       <c r="H44" s="81" t="str">
-        <f>SUM(H15,H40,H32,(H26*H10))</f>
+        <f>SUM(H15,H40,H32,(H26))</f>
         <v>0</v>
       </c>
       <c r="I44" s="81" t="str">
-        <f>SUM(C44:H44)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <f>SUM(I15,I40,I32,(I26))</f>
+        <v>0</v>
+      </c>
+      <c r="J44" s="81" t="str">
+        <f>SUM(J15,J40,J32,(J26))</f>
+        <v>0</v>
+      </c>
+      <c r="K44" s="81" t="str">
+        <f>SUM(C44:J44)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:15">
       <c r="B45" s="74" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C45" s="74">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="D45" s="74">
-        <v>717</v>
+        <v>390</v>
       </c>
       <c r="E45" s="74">
-        <v>65</v>
+        <v>199</v>
       </c>
       <c r="F45" s="74">
-        <v>86</v>
+        <v>265</v>
       </c>
       <c r="G45" s="74">
-        <v>60</v>
+        <v>300</v>
       </c>
       <c r="H45" s="74">
-        <v>86</v>
-      </c>
-      <c r="I45" s="74"/>
-    </row>
-    <row r="46" spans="1:13">
+        <v>275</v>
+      </c>
+      <c r="I45" s="74">
+        <v>520</v>
+      </c>
+      <c r="J45" s="74">
+        <v>140</v>
+      </c>
+      <c r="K45" s="74"/>
+    </row>
+    <row r="46" spans="1:15">
       <c r="B46" s="74" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C46" s="81" t="str">
-        <f>ROUND(SUM(C44/C45),2)</f>
+        <f>SUM(C44/C45)</f>
         <v>0</v>
       </c>
       <c r="D46" s="81" t="str">
-        <f>ROUND(SUM(D44/D45),2)</f>
+        <f>SUM(D44/D45)</f>
         <v>0</v>
       </c>
       <c r="E46" s="81" t="str">
-        <f>ROUND(SUM(E44/E45),2)</f>
+        <f>SUM(E44/E45)</f>
         <v>0</v>
       </c>
       <c r="F46" s="81" t="str">
-        <f>ROUND(SUM(F44/F45),2)</f>
+        <f>SUM(F44/F45)</f>
         <v>0</v>
       </c>
       <c r="G46" s="81" t="str">
-        <f>ROUND(SUM(G44/G45),2)</f>
+        <f>SUM(G44/G45)</f>
         <v>0</v>
       </c>
       <c r="H46" s="81" t="str">
-        <f>ROUND(SUM(H44/H45),2)</f>
-        <v>0</v>
-      </c>
-      <c r="I46" s="74"/>
-    </row>
-    <row r="47" spans="1:13">
+        <f>SUM(H44/H45)</f>
+        <v>0</v>
+      </c>
+      <c r="I46" s="81" t="str">
+        <f>SUM(I44/I45)</f>
+        <v>0</v>
+      </c>
+      <c r="J46" s="81" t="str">
+        <f>SUM(J44/J45)</f>
+        <v>0</v>
+      </c>
+      <c r="K46" s="74"/>
+    </row>
+    <row r="47" spans="1:15">
       <c r="B47" s="74" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C47" s="85" t="str">
-        <f>ROUND(C46*3.7,2)</f>
+        <f>C46*3.7</f>
         <v>0</v>
       </c>
       <c r="D47" s="85" t="str">
-        <f>ROUND(D46*3.7,2)</f>
+        <f>D46*3.7</f>
         <v>0</v>
       </c>
       <c r="E47" s="85" t="str">
-        <f>ROUND(E46*3.7,2)</f>
+        <f>E46*3.7</f>
         <v>0</v>
       </c>
       <c r="F47" s="85" t="str">
-        <f>ROUND(F46*3.7,2)</f>
+        <f>F46*3.7</f>
         <v>0</v>
       </c>
       <c r="G47" s="85" t="str">
-        <f>ROUND(G46*3.7,2)</f>
+        <f>G46*3.7</f>
         <v>0</v>
       </c>
       <c r="H47" s="85" t="str">
-        <f>ROUND(H46*3.7,2)</f>
-        <v>0</v>
-      </c>
-      <c r="I47" s="74"/>
+        <f>H46*3.7</f>
+        <v>0</v>
+      </c>
+      <c r="I47" s="85" t="str">
+        <f>I46*3.7</f>
+        <v>0</v>
+      </c>
+      <c r="J47" s="85" t="str">
+        <f>J46*3.7</f>
+        <v>0</v>
+      </c>
+      <c r="K47" s="74"/>
     </row>
   </sheetData>
   <sheetProtection sheet="false" objects="false" scenarios="false" formatCells="false" formatColumns="false" formatRows="false" insertColumns="false" insertRows="false" insertHyperlinks="false" deleteColumns="false" deleteRows="false" selectLockedCells="false" sort="false" autoFilter="false" pivotTables="false" selectUnlockedCells="false"/>
